--- a/exports/ADANIPOWER_full_report.xlsx
+++ b/exports/ADANIPOWER_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>10.34</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>22.05</v>
+        <v>20.7</v>
       </c>
       <c r="I2" t="n">
         <v>21.4632590775</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>2.56</v>
+        <v>-3.72</v>
       </c>
       <c r="L2" t="n">
         <v>7.67</v>
@@ -555,7 +578,7 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>4.96</v>
+        <v>6.58</v>
       </c>
       <c r="O2" t="n">
         <v>8</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>14.84</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44601.55208333334</v>
+        <v>44602.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>21.5</v>
+        <v>25.55</v>
       </c>
       <c r="I3" t="n">
         <v>23.1142121235775</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.86</v>
+        <v>-23.43</v>
       </c>
       <c r="L3" t="n">
-        <v>11.11</v>
+        <v>24.64</v>
       </c>
       <c r="M3" t="n">
         <v>1.42</v>
       </c>
       <c r="N3" t="n">
-        <v>3.64</v>
+        <v>14.42</v>
       </c>
       <c r="O3" t="n">
         <v>-6.58</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>20.02</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44658.55208333334</v>
+        <v>44659.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>46.5</v>
+        <v>44.2</v>
       </c>
       <c r="I4" t="n">
         <v>44.68642369898037</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K4" t="n">
-        <v>82</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>16.83</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>15.3</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44672.55208333334</v>
+        <v>44673.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>49.35</v>
+        <v>51.7</v>
       </c>
       <c r="I5" t="n">
         <v>50.28624712344331</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>-11.65</v>
+        <v>-16.97</v>
       </c>
       <c r="L5" t="n">
-        <v>11.65</v>
+        <v>17.19</v>
       </c>
       <c r="M5" t="n">
         <v>2.69</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.79</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44683.55208333334</v>
+        <v>44685.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>55.95</v>
+        <v>53.25</v>
       </c>
       <c r="I6" t="n">
         <v>53.87608510715671</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>8.220000000000001</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>3.68</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>19.26</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44697.55208333334</v>
+        <v>44698.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>53.45</v>
+        <v>56.15</v>
       </c>
       <c r="I7" t="n">
         <v>55.95089610455543</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.38</v>
+        <v>-5.45</v>
       </c>
       <c r="L7" t="n">
         <v>11.92</v>
       </c>
       <c r="M7" t="n">
-        <v>4.91</v>
+        <v>5.05</v>
       </c>
       <c r="N7" t="n">
         <v>5.07</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.22</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44713.55208333334</v>
+        <v>44714.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>61.4</v>
+        <v>59.6</v>
       </c>
       <c r="I8" t="n">
         <v>60.1837008245864</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K8" t="n">
-        <v>9.35</v>
+        <v>6.14</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>15.09</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44750.55208333334</v>
+        <v>44753.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>54.2</v>
+        <v>55.8</v>
       </c>
       <c r="I9" t="n">
         <v>55.66499715761591</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K9" t="n">
-        <v>9.06</v>
+        <v>6.38</v>
       </c>
       <c r="L9" t="n">
         <v>5.03</v>
@@ -954,7 +1061,7 @@
         <v>2.56</v>
       </c>
       <c r="N9" t="n">
-        <v>4.83</v>
+        <v>5.17</v>
       </c>
       <c r="O9" t="n">
         <v>-3.99</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44796.55208333334</v>
+        <v>44797.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>82.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>79.31294601997429</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K10" t="n">
-        <v>47.31</v>
+        <v>39.96</v>
       </c>
       <c r="L10" t="n">
         <v>3.32</v>
       </c>
       <c r="M10" t="n">
-        <v>2.66</v>
+        <v>4.99</v>
       </c>
       <c r="N10" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="O10" t="n">
         <v>5.17</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.48</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44872.55208333334</v>
+        <v>44874.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>69.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>71.2713548842102</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>75.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="K11" t="n">
-        <v>11.14</v>
+        <v>8.32</v>
       </c>
       <c r="L11" t="n">
         <v>7.23</v>
@@ -1068,7 +1199,7 @@
         <v>2.23</v>
       </c>
       <c r="N11" t="n">
-        <v>5.01</v>
+        <v>5.48</v>
       </c>
       <c r="O11" t="n">
         <v>-4.99</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44881.55208333334</v>
+        <v>44882.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>69.3</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>68.00033391073195</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.21</v>
+        <v>-5.52</v>
       </c>
       <c r="L12" t="n">
-        <v>4.4</v>
+        <v>6.56</v>
       </c>
       <c r="M12" t="n">
         <v>2.45</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44921.55208333334</v>
+        <v>44922.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>55.05</v>
+        <v>57.8</v>
       </c>
       <c r="I13" t="n">
         <v>56.75495534862364</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K13" t="n">
-        <v>18.63</v>
+        <v>14.56</v>
       </c>
       <c r="L13" t="n">
         <v>2.88</v>
@@ -1182,7 +1337,7 @@
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>-2.74</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>12.62</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44935.55208333334</v>
+        <v>44936.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>57.55</v>
+        <v>55.85</v>
       </c>
       <c r="I14" t="n">
         <v>55.87537847457211</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.43</v>
+        <v>-3.37</v>
       </c>
       <c r="L14" t="n">
         <v>6.23</v>
@@ -1239,7 +1406,7 @@
         <v>0.27</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="O14" t="n">
         <v>5</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>10.01</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44973.55208333334</v>
+        <v>44974.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>29.55</v>
+        <v>31.05</v>
       </c>
       <c r="I15" t="n">
         <v>30.89945376139092</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K15" t="n">
-        <v>47.09</v>
+        <v>44.4</v>
       </c>
       <c r="L15" t="n">
         <v>3.13</v>
       </c>
       <c r="M15" t="n">
-        <v>0.89</v>
+        <v>3.21</v>
       </c>
       <c r="N15" t="n">
-        <v>5.05</v>
+        <v>5.08</v>
       </c>
       <c r="O15" t="n">
         <v>-2.61</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44979.55208333334</v>
+        <v>44980.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>32.5</v>
+        <v>30.85</v>
       </c>
       <c r="I16" t="n">
         <v>31.59296511231004</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>4.67</v>
+        <v>-0.64</v>
       </c>
       <c r="L16" t="n">
         <v>2.74</v>
       </c>
       <c r="M16" t="n">
-        <v>-0</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>4.97</v>
+        <v>5.08</v>
       </c>
       <c r="O16" t="n">
         <v>5.08</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>11.66</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44985.55208333334</v>
+        <v>44986.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>29.25</v>
+        <v>30.7</v>
       </c>
       <c r="I17" t="n">
         <v>30.63389760847656</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>5.19</v>
+        <v>0.49</v>
       </c>
       <c r="L17" t="n">
         <v>2.76</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N17" t="n">
         <v>5.03</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>10.37</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44999.55208333334</v>
+        <v>45000.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>40.85</v>
+        <v>38.85</v>
       </c>
       <c r="I18" t="n">
         <v>39.5811289617376</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
-        <v>33.06</v>
+        <v>26.55</v>
       </c>
       <c r="L18" t="n">
         <v>0.33</v>
       </c>
       <c r="M18" t="n">
-        <v>1.53</v>
+        <v>4.9</v>
       </c>
       <c r="N18" t="n">
         <v>5</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.59</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45021.55208333334</v>
+        <v>45022.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>38</v>
+        <v>38.95</v>
       </c>
       <c r="I19" t="n">
         <v>38.89632320542752</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>2.19</v>
+        <v>-0.26</v>
       </c>
       <c r="L19" t="n">
         <v>10.42</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.75</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45064.38541666666</v>
+        <v>45064.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>45.85</v>
+        <v>45</v>
       </c>
       <c r="I20" t="n">
         <v>45.42575620291092</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K20" t="n">
-        <v>17.72</v>
+        <v>15.53</v>
       </c>
       <c r="L20" t="n">
         <v>4.88</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>7.69</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45065.55208333334</v>
+        <v>45068.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>47.25</v>
+        <v>49.6</v>
       </c>
       <c r="I21" t="n">
         <v>47.25874898720626</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-5</v>
+        <v>-10.22</v>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
+        <v>10.22</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.57</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45098.55208333334</v>
+        <v>45099.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>52.2</v>
+        <v>51.35</v>
       </c>
       <c r="I22" t="n">
         <v>51.39991978984818</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K22" t="n">
-        <v>5.24</v>
+        <v>3.53</v>
       </c>
       <c r="L22" t="n">
         <v>1.81</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.09</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45132.38541666666</v>
+        <v>45132.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>48.35</v>
+        <v>52.35</v>
       </c>
       <c r="I23" t="n">
         <v>49.95876923365262</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K23" t="n">
-        <v>5.84</v>
+        <v>-1.95</v>
       </c>
       <c r="L23" t="n">
         <v>2.53</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>10.71</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45205.55208333334</v>
+        <v>45208.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>72.7</v>
+        <v>68.5</v>
       </c>
       <c r="I24" t="n">
         <v>72.32846298631014</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>73</v>
+        <v>75.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>38.87</v>
+        <v>30.85</v>
       </c>
       <c r="L24" t="n">
         <v>8.119999999999999</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45225.55208333334</v>
+        <v>45226.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>66</v>
+        <v>69.25</v>
       </c>
       <c r="I25" t="n">
         <v>66.75113537685159</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K25" t="n">
-        <v>3.65</v>
+        <v>-1.09</v>
       </c>
       <c r="L25" t="n">
         <v>4.74</v>
@@ -1866,7 +2165,7 @@
         <v>3.07</v>
       </c>
       <c r="N25" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="O25" t="n">
         <v>-6.4</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>14.32</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45309.55208333334</v>
+        <v>45310.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I26" t="n">
         <v>104.1889252852968</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>83.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K26" t="n">
-        <v>53.07</v>
+        <v>50.18</v>
       </c>
       <c r="L26" t="n">
         <v>4.26</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>7.11</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45316.55208333334</v>
+        <v>45320.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>108.65</v>
+        <v>112.8</v>
       </c>
       <c r="I27" t="n">
         <v>111.3917397076856</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.47</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>6.73</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>1.27</v>
+        <v>4.92</v>
       </c>
       <c r="N27" t="n">
-        <v>3.48</v>
+        <v>5.02</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>110.6</v>
+        <v>105.65</v>
       </c>
       <c r="I28" t="n">
         <v>106.5964573526548</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.95</v>
+        <v>-6.34</v>
       </c>
       <c r="L28" t="n">
         <v>8.289999999999999</v>
@@ -2037,7 +2372,7 @@
         <v>2.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.87</v>
+        <v>4.48</v>
       </c>
       <c r="O28" t="n">
         <v>5.02</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>11.58</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>106.4</v>
+        <v>112.1</v>
       </c>
       <c r="I29" t="n">
         <v>112.092268639825</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.71</v>
+        <v>-6.11</v>
       </c>
       <c r="L29" t="n">
-        <v>5.82</v>
+        <v>6.11</v>
       </c>
       <c r="M29" t="n">
-        <v>1.68</v>
+        <v>2.96</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>5.36</v>
       </c>
       <c r="O29" t="n">
         <v>-4.48</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.01</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>117.7</v>
+        <v>115.5</v>
       </c>
       <c r="I30" t="n">
         <v>117.5050236435056</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K30" t="n">
-        <v>5</v>
+        <v>3.03</v>
       </c>
       <c r="L30" t="n">
         <v>2.85</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45425.55208333334</v>
+        <v>45426.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>118.65</v>
+        <v>126.25</v>
       </c>
       <c r="I31" t="n">
         <v>123.0172689124543</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.73</v>
+        <v>-9.31</v>
       </c>
       <c r="L31" t="n">
-        <v>9.26</v>
+        <v>10.13</v>
       </c>
       <c r="M31" t="n">
         <v>0.9</v>
       </c>
       <c r="N31" t="n">
-        <v>4.66</v>
+        <v>5.39</v>
       </c>
       <c r="O31" t="n">
         <v>-1.53</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>12.05</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>175.4</v>
+        <v>151.4</v>
       </c>
       <c r="I32" t="n">
         <v>155.2246169970347</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K32" t="n">
-        <v>38.93</v>
+        <v>19.92</v>
       </c>
       <c r="L32" t="n">
         <v>6.46</v>
       </c>
       <c r="M32" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="N32" t="n">
-        <v>4.18</v>
+        <v>17.9</v>
       </c>
       <c r="O32" t="n">
         <v>5.39</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>23.53</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45481.55208333334</v>
+        <v>45482.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>139.55</v>
+        <v>146</v>
       </c>
       <c r="I33" t="n">
         <v>145.8748686518853</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K33" t="n">
-        <v>7.83</v>
+        <v>3.57</v>
       </c>
       <c r="L33" t="n">
         <v>15.32</v>
@@ -2322,7 +2717,7 @@
         <v>3.73</v>
       </c>
       <c r="N33" t="n">
-        <v>3.73</v>
+        <v>4.3</v>
       </c>
       <c r="O33" t="n">
         <v>-17.9</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.19</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45509.38541666666</v>
+        <v>45509.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>139.15</v>
+        <v>137.4</v>
       </c>
       <c r="I34" t="n">
         <v>138.3640374926021</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.69</v>
+        <v>-5.89</v>
       </c>
       <c r="L34" t="n">
         <v>11.44</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>9.15</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45548.55208333334</v>
+        <v>45551.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>126.8</v>
+        <v>134.75</v>
       </c>
       <c r="I35" t="n">
         <v>133.4814489386392</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>39</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K35" t="n">
-        <v>7.71</v>
+        <v>1.93</v>
       </c>
       <c r="L35" t="n">
         <v>2.87</v>
       </c>
       <c r="M35" t="n">
-        <v>2.23</v>
+        <v>4.26</v>
       </c>
       <c r="N35" t="n">
         <v>5.85</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>128</v>
+        <v>123.7</v>
       </c>
       <c r="I36" t="n">
         <v>126.5893791564278</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.01</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>6.27</v>
+        <v>8.94</v>
       </c>
       <c r="M36" t="n">
         <v>1.39</v>
       </c>
       <c r="N36" t="n">
-        <v>1.77</v>
+        <v>2.34</v>
       </c>
       <c r="O36" t="n">
         <v>5.28</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45622.55208333334</v>
+        <v>45623.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>87.75</v>
+        <v>101.95</v>
       </c>
       <c r="I37" t="n">
         <v>101.6018573686169</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K37" t="n">
-        <v>29.06</v>
+        <v>17.58</v>
       </c>
       <c r="L37" t="n">
         <v>4.93</v>
@@ -2550,7 +2993,7 @@
         <v>2.65</v>
       </c>
       <c r="N37" t="n">
-        <v>3.43</v>
+        <v>19.72</v>
       </c>
       <c r="O37" t="n">
         <v>-2.34</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>24.12</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45650.38541666666</v>
+        <v>45650.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>100.55</v>
+        <v>99.2</v>
       </c>
       <c r="I38" t="n">
         <v>99.3291548524698</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.37</v>
+        <v>-2.7</v>
       </c>
       <c r="L38" t="n">
         <v>15.2</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>7.88</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45656.38541666666</v>
+        <v>45656.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>102.6</v>
+        <v>108.6</v>
       </c>
       <c r="I39" t="n">
         <v>107.012927016549</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.43</v>
+        <v>-9.48</v>
       </c>
       <c r="L39" t="n">
-        <v>4.69</v>
+        <v>12.7</v>
       </c>
       <c r="M39" t="n">
         <v>0.6899999999999999</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>11.22</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>99.59999999999999</v>
+        <v>97.45</v>
       </c>
       <c r="I40" t="n">
         <v>97.77730312728659</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>-8.289999999999999</v>
+        <v>-10.27</v>
       </c>
       <c r="L40" t="n">
-        <v>8.66</v>
+        <v>11.88</v>
       </c>
       <c r="M40" t="n">
         <v>1.84</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>8.35</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45670.55208333334</v>
+        <v>45671.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>90.5</v>
+        <v>105.25</v>
       </c>
       <c r="I41" t="n">
         <v>98.76162048095902</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>7.13</v>
+        <v>-8</v>
       </c>
       <c r="L41" t="n">
-        <v>3.23</v>
+        <v>10.06</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>19.28</v>
       </c>
       <c r="O41" t="n">
         <v>-3.11</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>16.97</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>103.1</v>
+        <v>100.05</v>
       </c>
       <c r="I42" t="n">
         <v>100.6710307221985</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.04</v>
+        <v>-4.94</v>
       </c>
       <c r="L42" t="n">
         <v>12.59</v>
       </c>
       <c r="M42" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="N42" t="n">
-        <v>2.4</v>
+        <v>3.78</v>
       </c>
       <c r="O42" t="n">
         <v>19.28</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>11.31</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45712.55208333334</v>
+        <v>45713.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>93.8</v>
+        <v>101.3</v>
       </c>
       <c r="I43" t="n">
         <v>100.5113525687887</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K43" t="n">
-        <v>6.25</v>
+        <v>-1.25</v>
       </c>
       <c r="L43" t="n">
         <v>7.3</v>
@@ -2892,7 +3407,7 @@
         <v>2.29</v>
       </c>
       <c r="N43" t="n">
-        <v>4.92</v>
+        <v>5.86</v>
       </c>
       <c r="O43" t="n">
         <v>-3.78</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.37</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45742.38541666666</v>
+        <v>45742.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>100.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I44" t="n">
         <v>99.5789601311623</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.79</v>
+        <v>-1.88</v>
       </c>
       <c r="L44" t="n">
         <v>7.31</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.06</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45751.38541666666</v>
+        <v>45751.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>104.75</v>
+        <v>106.6</v>
       </c>
       <c r="I45" t="n">
         <v>106.41538258215</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.38</v>
+        <v>-7.24</v>
       </c>
       <c r="L45" t="n">
         <v>8.65</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.16</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45776.55208333334</v>
+        <v>45777.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>109.8</v>
+        <v>108.4</v>
       </c>
       <c r="I46" t="n">
         <v>108.7472329006732</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>3</v>
+        <v>1.69</v>
       </c>
       <c r="L46" t="n">
         <v>13.32</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.81</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45793.38541666666</v>
+        <v>45793.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>111.35</v>
+        <v>113.2</v>
       </c>
       <c r="I47" t="n">
         <v>111.406657120725</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.72</v>
+        <v>-4.43</v>
       </c>
       <c r="L47" t="n">
         <v>7.8</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.25</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45825.55208333334</v>
+        <v>45826.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>111.6</v>
+        <v>110.4</v>
       </c>
       <c r="I48" t="n">
         <v>111.5846067595503</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>32</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.41</v>
+        <v>-2.47</v>
       </c>
       <c r="L48" t="n">
         <v>6.23</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>7.2</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45834.38541666666</v>
+        <v>45834.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>113.95</v>
+        <v>115.8</v>
       </c>
       <c r="I49" t="n">
         <v>114.1033934588538</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.22</v>
+        <v>-4.89</v>
       </c>
       <c r="L49" t="n">
-        <v>3.89</v>
+        <v>5.16</v>
       </c>
       <c r="M49" t="n">
         <v>1.3</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>6.57</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>117</v>
+        <v>115.15</v>
       </c>
       <c r="I50" t="n">
         <v>116.2710503851107</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>1.04</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L50" t="n">
         <v>1.73</v>
       </c>
       <c r="M50" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="N50" t="n">
-        <v>1.63</v>
+        <v>2.39</v>
       </c>
       <c r="O50" t="n">
         <v>3.67</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>4.83</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45880.38541666666</v>
+        <v>45880.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>115.55</v>
+        <v>119.4</v>
       </c>
       <c r="I51" t="n">
         <v>118.7923332871889</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.35</v>
+        <v>-3.69</v>
       </c>
       <c r="L51" t="n">
         <v>4.6</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.93</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>163.25</v>
+        <v>151.65</v>
       </c>
       <c r="I52" t="n">
         <v>153.6736335459216</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>43</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K52" t="n">
-        <v>36.73</v>
+        <v>27.01</v>
       </c>
       <c r="L52" t="n">
         <v>3.43</v>
@@ -3405,7 +4028,7 @@
         <v>0.67</v>
       </c>
       <c r="N52" t="n">
-        <v>4.11</v>
+        <v>11.24</v>
       </c>
       <c r="O52" t="n">
         <v>3.83</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>18.58</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45946.55208333334</v>
+        <v>45947.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>156.5</v>
+        <v>163.7</v>
       </c>
       <c r="I53" t="n">
         <v>160.3276726425842</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.2</v>
+        <v>-7.95</v>
       </c>
       <c r="L53" t="n">
-        <v>7.95</v>
+        <v>10.78</v>
       </c>
       <c r="M53" t="n">
         <v>1.33</v>
       </c>
       <c r="N53" t="n">
-        <v>5.52</v>
+        <v>6.16</v>
       </c>
       <c r="O53" t="n">
         <v>-11.24</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45964.38541666666</v>
+        <v>45964.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>158.04</v>
+        <v>156.8</v>
       </c>
       <c r="I54" t="n">
         <v>157.5565116624276</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.46</v>
+        <v>-4.22</v>
       </c>
       <c r="L54" t="n">
-        <v>4.23</v>
+        <v>4.64</v>
       </c>
       <c r="M54" t="n">
         <v>0.47</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.9</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46022.55208333334</v>
+        <v>46023.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>142.9</v>
+        <v>148.93</v>
       </c>
       <c r="I55" t="n">
         <v>145.3520322939698</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>58</v>
+        <v>58.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>8.859999999999999</v>
+        <v>5.02</v>
       </c>
       <c r="L55" t="n">
         <v>1.72</v>
@@ -3576,7 +4235,7 @@
         <v>0.9</v>
       </c>
       <c r="N55" t="n">
-        <v>2.76</v>
+        <v>4.06</v>
       </c>
       <c r="O55" t="n">
         <v>-0.73</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.31</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46041.38541666666</v>
+        <v>46041.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>141.13</v>
+        <v>140.3</v>
       </c>
       <c r="I56" t="n">
         <v>140.7043639249652</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.24</v>
+        <v>-5.79</v>
       </c>
       <c r="L56" t="n">
         <v>6.31</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>4.74</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>134.5</v>
+        <v>146.25</v>
       </c>
       <c r="I57" t="n">
         <v>142.696560526562</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>4.13</v>
+        <v>-4.24</v>
       </c>
       <c r="L57" t="n">
-        <v>1.85</v>
+        <v>6.23</v>
       </c>
       <c r="M57" t="n">
-        <v>1.47</v>
+        <v>7.81</v>
       </c>
       <c r="N57" t="n">
-        <v>2.6</v>
+        <v>7.43</v>
       </c>
       <c r="O57" t="n">
         <v>-1.41</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>10.44</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46066.38541666666</v>
+        <v>46066.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>141.6</v>
+        <v>140.2</v>
       </c>
       <c r="I58" t="n">
         <v>140.3541563168736</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.18</v>
+        <v>-4.14</v>
       </c>
       <c r="L58" t="n">
-        <v>3.92</v>
+        <v>4.89</v>
       </c>
       <c r="M58" t="n">
         <v>0.49</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>8.1</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46092.55208333334</v>
+        <v>46093.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>139.2</v>
+        <v>145.7</v>
       </c>
       <c r="I59" t="n">
         <v>143.9642789940887</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>0.71</v>
+        <v>-3.92</v>
       </c>
       <c r="L59" t="n">
-        <v>4.44</v>
+        <v>8.4</v>
       </c>
       <c r="M59" t="n">
         <v>1.5</v>
       </c>
       <c r="N59" t="n">
-        <v>1.88</v>
+        <v>7.54</v>
       </c>
       <c r="O59" t="n">
         <v>-6.31</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>222.77</v>
+        <v>212.41</v>
       </c>
       <c r="I60" t="n">
         <v>214.3212752957434</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K60" t="n">
-        <v>52.9</v>
+        <v>45.79</v>
       </c>
       <c r="L60" t="n">
         <v>5.62</v>
@@ -3861,7 +4580,7 @@
         <v>2.01</v>
       </c>
       <c r="N60" t="n">
-        <v>3.19</v>
+        <v>5.28</v>
       </c>
       <c r="O60" t="n">
         <v>7.54</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>11.13</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>219.59</v>
+        <v>232.2</v>
       </c>
       <c r="I61" t="n">
         <v>228.3539516304993</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.38</v>
+        <v>-9.32</v>
       </c>
       <c r="L61" t="n">
-        <v>7.81</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M61" t="n">
         <v>2.19</v>
       </c>
       <c r="N61" t="n">
-        <v>5.18</v>
+        <v>6.62</v>
       </c>
       <c r="O61" t="n">
         <v>-5.28</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46174.55208333334</v>
+        <v>46175.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>233</v>
+        <v>231.6</v>
       </c>
       <c r="I62" t="n">
         <v>231.8873298638262</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K62" t="n">
-        <v>0.34</v>
+        <v>-0.26</v>
       </c>
       <c r="L62" t="n">
         <v>5.12</v>
       </c>
       <c r="M62" t="n">
-        <v>-0</v>
+        <v>1.29</v>
       </c>
       <c r="N62" t="n">
         <v>4.41</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>7.9</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46191.38541666666</v>
+        <v>46191.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>228.85</v>
+        <v>231.7</v>
       </c>
       <c r="I63" t="n">
         <v>231.3539773180333</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K63" t="n">
-        <v>1.19</v>
+        <v>-0.04</v>
       </c>
       <c r="L63" t="n">
         <v>2.4</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>7.56</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46209.55208333334</v>
+        <v>46210.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>220.1</v>
+        <v>216.91</v>
       </c>
       <c r="I64" t="n">
         <v>218.1931434451273</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.01</v>
+        <v>-6.38</v>
       </c>
       <c r="L64" t="n">
-        <v>5.87</v>
+        <v>6.65</v>
       </c>
       <c r="M64" t="n">
         <v>0.38</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>7.55</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46260.55208333334</v>
+        <v>46261.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>208.05</v>
+        <v>214.87</v>
       </c>
       <c r="I65" t="n">
         <v>210.3572006278959</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K65" t="n">
-        <v>4.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L65" t="n">
         <v>5.55</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>6.25</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46265.38541666666</v>
+        <v>46265.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>208.07</v>
+        <v>204</v>
       </c>
       <c r="I66" t="n">
         <v>204.6673993011104</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.16</v>
+        <v>-5.06</v>
       </c>
       <c r="L66" t="n">
-        <v>3.94</v>
+        <v>6.18</v>
       </c>
       <c r="M66" t="n">
         <v>-0</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>6.67</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46273.55208333334</v>
+        <v>46274.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>208</v>
+        <v>214.7</v>
       </c>
       <c r="I67" t="n">
         <v>214.5957635312373</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.96</v>
+        <v>-5.25</v>
       </c>
       <c r="L67" t="n">
-        <v>3.59</v>
+        <v>5.81</v>
       </c>
       <c r="M67" t="n">
         <v>1.01</v>
       </c>
       <c r="N67" t="n">
-        <v>1.77</v>
+        <v>2.88</v>
       </c>
       <c r="O67" t="n">
         <v>-3.82</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>7.13</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46280.38541666666</v>
+        <v>46280.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>204.2</v>
+        <v>202</v>
       </c>
       <c r="I68" t="n">
         <v>203.4845760471552</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>-4.89</v>
+        <v>-5.92</v>
       </c>
       <c r="L68" t="n">
-        <v>4.98</v>
+        <v>6.19</v>
       </c>
       <c r="M68" t="n">
         <v>0.47</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.14</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46310.55208333334</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>195.73</v>
+        <v>196.95</v>
       </c>
       <c r="I69" t="n">
         <v>196.7157077596275</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K69" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="L69" t="n">
         <v>4.23</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>7.17</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>184.8</v>
+        <v>175.83</v>
       </c>
       <c r="I70" t="n">
         <v>184.5092581675158</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K70" t="n">
-        <v>-6.17</v>
+        <v>-10.72</v>
       </c>
       <c r="L70" t="n">
-        <v>7.08</v>
+        <v>10.99</v>
       </c>
       <c r="M70" t="n">
         <v>0.38</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,12 @@
       <c r="Q71" t="n">
         <v>6</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7450,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.3</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7460,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7480,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50.2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -6653,7 +7510,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -6663,7 +7520,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6673,7 +7530,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6683,7 +7540,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.39</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7550,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.85</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7560,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.84</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7570,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>82</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7580,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.6</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7590,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.06</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7600,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.03</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7610,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.83</v>
+        <v>24.64</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7620,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7630,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7640,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="25">
@@ -6803,7 +7660,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.29</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7670,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.35</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7680,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
